--- a/Firmware/RRF/Valkyrie Connection Table.xlsx
+++ b/Firmware/RRF/Valkyrie Connection Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/Firmware/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1132" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{991C164D-5A6C-4632-B879-4F48E4E7B2B3}"/>
+  <xr:revisionPtr revIDLastSave="1143" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0929DD41-401E-405E-88BA-46B8100C4C16}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
   <sheets>
     <sheet name="DUET 3 6HC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="416">
   <si>
     <t>Type</t>
   </si>
@@ -440,6 +440,12 @@
     <t>Octopus Pro pin assignment</t>
   </si>
   <si>
+    <t>Heated Bed</t>
+  </si>
+  <si>
+    <t>chamber heater</t>
+  </si>
+  <si>
     <t>device assignment</t>
   </si>
   <si>
@@ -473,6 +479,15 @@
     <t>notes</t>
   </si>
   <si>
+    <t>6pin R</t>
+  </si>
+  <si>
+    <t>6 pin M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 pin </t>
+  </si>
+  <si>
     <t> </t>
   </si>
   <si>
@@ -491,6 +506,9 @@
     <t>Gnd</t>
   </si>
   <si>
+    <t>Pin x.x</t>
+  </si>
+  <si>
     <t>dry bosx S3</t>
   </si>
   <si>
@@ -518,6 +536,9 @@
     <t>e1temp</t>
   </si>
   <si>
+    <t xml:space="preserve">Pin x ,x </t>
+  </si>
+  <si>
     <t>Chamber thermister S2</t>
   </si>
   <si>
@@ -798,6 +819,9 @@
   </si>
   <si>
     <t>e2heat</t>
+  </si>
+  <si>
+    <t>pin x ,x ,x</t>
   </si>
   <si>
     <t>HE3</t>
@@ -1270,7 +1294,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1639,7 +1663,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1816,9 +1840,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1856,7 +1880,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1962,7 +1986,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2104,7 +2128,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3895,7 +3919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10D3F89-6631-4EDE-8E63-7F58B672DC4B}">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -3903,10 +3927,12 @@
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.28515625" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="8"/>
       <c r="B1" s="18" t="s">
         <v>131</v>
@@ -3922,7 +3948,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="28"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:15">
       <c r="A2" s="8"/>
       <c r="B2" s="19" t="s">
         <v>132</v>
@@ -3937,1685 +3963,1712 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="28"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" t="s">
+        <v>133</v>
+      </c>
+      <c r="N2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="8"/>
       <c r="B3" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>145</v>
+      </c>
+      <c r="M3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L4" s="29"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="20" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L5" s="29"/>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="20" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="8"/>
       <c r="B7" s="20" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>160</v>
+      </c>
+      <c r="O7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="8"/>
       <c r="B8" s="20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K8" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L8" s="29"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:15">
       <c r="A9" s="8"/>
       <c r="B9" s="20" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L9" s="29"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:15">
       <c r="A10" s="8"/>
       <c r="B10" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L10" s="29"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:15">
       <c r="A11" s="8"/>
       <c r="B11" s="20" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="8"/>
       <c r="B12" s="20" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="8"/>
       <c r="B13" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L13" s="29"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:15">
       <c r="A14" s="8"/>
       <c r="B14" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L14" s="29"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:15">
       <c r="A15" s="8"/>
       <c r="B15" s="20" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L15" s="29"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:15">
       <c r="A16" s="8"/>
       <c r="B16" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L16" s="29"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:15">
       <c r="A17" s="8"/>
       <c r="B17" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L17" s="29"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:15">
       <c r="A18" s="8"/>
       <c r="B18" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L18" s="29"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:15">
       <c r="A19" s="8"/>
       <c r="B19" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>179</v>
-      </c>
       <c r="G19" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L19" s="29"/>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:15">
       <c r="A20" s="8"/>
       <c r="B20" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:15">
       <c r="A21" s="8"/>
       <c r="B21" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L21" s="29"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:15">
       <c r="A22" s="8"/>
       <c r="B22" s="24" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L22" s="29"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:15">
       <c r="A23" s="8"/>
       <c r="B23" s="25"/>
       <c r="C23" s="22" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="20" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K24" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L24" s="29"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="20" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I25" s="22"/>
       <c r="J25" s="22"/>
       <c r="K25" s="27"/>
       <c r="L25" s="29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="20" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="20" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L27" s="29"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="20" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K28" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L28" s="29"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="O28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="20" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L29" s="29"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="20" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K30" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L30" s="29"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="20" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L31" s="29"/>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="8"/>
       <c r="B33" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K33" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="8"/>
       <c r="B34" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K34" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L34" s="29"/>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:14">
       <c r="A35" s="8"/>
       <c r="B35" s="20" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K35" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="8"/>
       <c r="B36" s="20" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K36" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L36" s="29"/>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:14">
       <c r="A37" s="8"/>
       <c r="B37" s="20" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C37" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F37" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="D37" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>243</v>
-      </c>
       <c r="G37" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K37" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L37" s="29"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="N37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="8"/>
       <c r="B38" s="20" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K38" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L38" s="29"/>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:14">
       <c r="A39" s="8"/>
       <c r="B39" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K39" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L39" s="29"/>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:14">
       <c r="A40" s="8"/>
       <c r="B40" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K40" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L40" s="29" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="8"/>
       <c r="B41" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K41" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L41" s="29" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="8"/>
       <c r="B42" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K42" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L42" s="29"/>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:14">
       <c r="A43" s="8"/>
       <c r="B43" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K43" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L43" s="29"/>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:14">
       <c r="A44" s="8"/>
       <c r="B44" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K44" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L44" s="29"/>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:14">
       <c r="A45" s="8"/>
       <c r="B45" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K45" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L45" s="29"/>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:14">
       <c r="A46" s="8"/>
       <c r="B46" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K46" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L46" s="29"/>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:14">
       <c r="A47" s="8"/>
       <c r="B47" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K47" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L47" s="29"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:14">
       <c r="A48" s="8"/>
       <c r="B48" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K48" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L48" s="29"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="8"/>
       <c r="B49" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K49" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L49" s="29"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="8"/>
       <c r="B50" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K50" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L50" s="29"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="8"/>
       <c r="B51" s="20" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K51" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L51" s="29"/>
     </row>
@@ -5625,31 +5678,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K52" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L52" s="29"/>
     </row>
@@ -5659,446 +5712,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J53" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K53" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L53" s="29"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="8"/>
       <c r="B54" s="20" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K54" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L54" s="29"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="8"/>
       <c r="B55" s="20" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K55" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L55" s="29"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="8"/>
       <c r="B56" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K56" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L56" s="29"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="8"/>
       <c r="B57" s="20" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K57" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L57" s="29"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="8"/>
       <c r="B58" s="20" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J58" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K58" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L58" s="29"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="8"/>
       <c r="B59" s="20" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J59" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K59" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L59" s="29"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="8"/>
       <c r="B60" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K60" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L60" s="29"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="8"/>
       <c r="B61" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K61" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L61" s="29"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="8"/>
       <c r="B62" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K62" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L62" s="29"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="8"/>
       <c r="B63" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="H63" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>282</v>
-      </c>
       <c r="J63" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K63" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L63" s="29"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="8"/>
       <c r="B64" s="20" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J64" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K64" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L64" s="29"/>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="8"/>
       <c r="B65" s="20" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K65" s="27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L65" s="29"/>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="8"/>
       <c r="B66" s="24" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -6322,13 +6375,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="E1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -6337,12 +6390,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
         <v>69</v>
@@ -6353,12 +6406,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
@@ -6369,12 +6422,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
@@ -6388,15 +6441,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
@@ -6407,12 +6460,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -6425,7 +6478,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
@@ -6438,7 +6491,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
@@ -6451,7 +6504,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -6464,7 +6517,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -6476,7 +6529,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C11" t="s">
         <v>72</v>
@@ -6985,13 +7038,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -7000,13 +7053,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -7015,13 +7068,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -7030,13 +7083,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -7045,13 +7098,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -7060,13 +7113,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -7075,13 +7128,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -7090,25 +7143,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -7123,7 +7176,7 @@
         <v>69</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -7138,43 +7191,43 @@
         <v>72</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -7186,10 +7239,10 @@
         <v>69</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -7200,10 +7253,10 @@
         <v>72</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -7214,10 +7267,10 @@
         <v>69</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -7228,10 +7281,10 @@
         <v>72</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -7242,10 +7295,10 @@
         <v>69</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7256,10 +7309,10 @@
         <v>72</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7270,10 +7323,10 @@
         <v>69</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7284,10 +7337,10 @@
         <v>72</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7298,10 +7351,10 @@
         <v>69</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -7312,10 +7365,10 @@
         <v>72</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -7326,10 +7379,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7340,10 +7393,10 @@
         <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7354,10 +7407,10 @@
         <v>69</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7368,10 +7421,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -7382,10 +7435,10 @@
         <v>69</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -7396,10 +7449,10 @@
         <v>72</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -7410,10 +7463,10 @@
         <v>69</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -7424,10 +7477,10 @@
         <v>72</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -7438,10 +7491,10 @@
         <v>69</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -7452,10 +7505,10 @@
         <v>72</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -7469,7 +7522,7 @@
         <v>85</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -7483,758 +7536,758 @@
         <v>85</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C80" t="s">
         <v>72</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C81" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C82" t="s">
         <v>69</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C83" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C85" t="s">
         <v>69</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C86" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C87" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C88" t="s">
         <v>69</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C89" t="s">
         <v>72</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C90" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C91" t="s">
         <v>69</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C92" t="s">
         <v>72</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C93" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C94" t="s">
         <v>69</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C95" t="s">
         <v>72</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C96" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C97" t="s">
         <v>69</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C98" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C99" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C101" t="s">
         <v>72</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C102" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C103" t="s">
         <v>69</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E103" s="32"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C104" t="s">
         <v>72</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C105" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C106" t="s">
         <v>69</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E106" s="32"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C107" t="s">
         <v>72</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C108" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E108" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C109" t="s">
         <v>69</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E109" s="32"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C110" t="s">
         <v>72</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C111" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C112" t="s">
         <v>69</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C113" t="s">
         <v>72</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C114" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E114" s="32" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C115" t="s">
         <v>69</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C116" t="s">
         <v>72</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C117" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C119" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C120" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C122" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D123" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C125" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D125" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C126" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D126" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C127" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D127" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C128" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D128" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C129" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D129" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D130" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D131" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C132" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D132" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C135" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D135" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C136" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D136" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C137" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D137" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C139" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D139" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -8762,7 +8815,7 @@
         <v>85</v>
       </c>
       <c r="B186" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C186" t="s">
         <v>69</v>
@@ -8779,7 +8832,7 @@
         <v>85</v>
       </c>
       <c r="B187" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C187" t="s">
         <v>72</v>
@@ -8833,7 +8886,7 @@
         <v>94</v>
       </c>
       <c r="C190" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>92</v>
@@ -9289,71 +9342,71 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="12" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -9361,13 +9414,13 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -9375,7 +9428,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H5" s="8"/>
     </row>
@@ -9384,16 +9437,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H6" s="8"/>
     </row>
@@ -9402,16 +9455,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -9420,16 +9473,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H8" s="8"/>
     </row>
@@ -9438,16 +9491,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -9456,16 +9509,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="13" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H10" s="8"/>
     </row>
@@ -9474,16 +9527,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="13" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -9492,16 +9545,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H12" s="8"/>
     </row>
@@ -9510,16 +9563,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H13" s="8"/>
     </row>
@@ -9528,16 +9581,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -9546,22 +9599,22 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9569,23 +9622,23 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="11" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H17" s="8"/>
     </row>
@@ -9594,18 +9647,18 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H18" s="8"/>
     </row>
@@ -9614,18 +9667,18 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H19" s="8"/>
     </row>
@@ -9634,20 +9687,20 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H20" s="8"/>
     </row>
@@ -9656,20 +9709,20 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H21" s="8"/>
     </row>
@@ -9678,20 +9731,20 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H22" s="8"/>
     </row>
@@ -9700,44 +9753,44 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H24" s="8"/>
     </row>

--- a/Firmware/RRF/Valkyrie Connection Table.xlsx
+++ b/Firmware/RRF/Valkyrie Connection Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/Firmware/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1143" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0929DD41-401E-405E-88BA-46B8100C4C16}"/>
+  <xr:revisionPtr revIDLastSave="1158" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39160140-E775-4DB6-BE42-C7BD3CC79B01}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
   <sheets>
     <sheet name="DUET 3 6HC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="421">
   <si>
     <t>Type</t>
   </si>
@@ -446,6 +446,9 @@
     <t>chamber heater</t>
   </si>
   <si>
+    <t xml:space="preserve">other </t>
+  </si>
+  <si>
     <t>device assignment</t>
   </si>
   <si>
@@ -536,21 +539,21 @@
     <t>e1temp</t>
   </si>
   <si>
+    <t>Chamber thermister S2</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>PF6</t>
+  </si>
+  <si>
+    <t>e2temp</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pin x ,x </t>
   </si>
   <si>
-    <t>Chamber thermister S2</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>PF6</t>
-  </si>
-  <si>
-    <t>e2temp</t>
-  </si>
-  <si>
     <t xml:space="preserve">stepper motor temperature </t>
   </si>
   <si>
@@ -743,7 +746,7 @@
     <t>fan3</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Chamber Fan</t>
   </si>
   <si>
     <t>Fan 4</t>
@@ -755,6 +758,9 @@
     <t>fan4</t>
   </si>
   <si>
+    <t>Pin x,x</t>
+  </si>
+  <si>
     <t>Part cooling</t>
   </si>
   <si>
@@ -797,6 +803,9 @@
     <t xml:space="preserve">bed heater ssr </t>
   </si>
   <si>
+    <t>Pin Lx,Nx,Ex,</t>
+  </si>
+  <si>
     <t>hotend</t>
   </si>
   <si>
@@ -821,9 +830,6 @@
     <t>e2heat</t>
   </si>
   <si>
-    <t>pin x ,x ,x</t>
-  </si>
-  <si>
     <t>HE3</t>
   </si>
   <si>
@@ -954,6 +960,15 @@
   </si>
   <si>
     <t xml:space="preserve">Dry box </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED s  chamber </t>
+  </si>
+  <si>
+    <t>Anviz</t>
+  </si>
+  <si>
+    <t>Pin  x,x</t>
   </si>
   <si>
     <t xml:space="preserve">ident </t>
@@ -1296,7 +1311,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1342,6 +1357,12 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Helvetica Neue"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1616,7 +1637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1678,6 +1699,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3927,9 +3949,13 @@
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="34.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3969,196 +3995,196 @@
       <c r="N2" t="s">
         <v>134</v>
       </c>
+      <c r="O2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="8"/>
       <c r="B3" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>152</v>
-      </c>
       <c r="G5" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L5" s="29"/>
       <c r="M5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E6" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>158</v>
-      </c>
       <c r="G6" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="8"/>
       <c r="B7" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="29" t="s">
         <v>161</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="O7" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -4179,431 +4205,434 @@
         <v>168</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K8" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L8" s="29"/>
+      <c r="O8" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="8"/>
       <c r="B9" s="20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E9" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>172</v>
-      </c>
       <c r="G9" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L9" s="29"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="8"/>
       <c r="B10" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L10" s="29"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="8"/>
       <c r="B11" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="8"/>
       <c r="B12" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="8"/>
       <c r="B13" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L13" s="29"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="8"/>
       <c r="B14" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L14" s="29"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="8"/>
       <c r="B15" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L15" s="29"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="8"/>
       <c r="B16" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E16" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>184</v>
-      </c>
       <c r="I16" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L16" s="29"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="8"/>
       <c r="B17" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" s="22" t="s">
+      <c r="G17" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="I17" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L17" s="29"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="8"/>
       <c r="B18" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E18" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>191</v>
-      </c>
       <c r="I18" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="8"/>
       <c r="B19" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E19" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>194</v>
-      </c>
       <c r="I19" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L19" s="29"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="8"/>
       <c r="B20" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E20" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>197</v>
-      </c>
       <c r="I20" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L20" s="29"/>
     </row>
@@ -4613,65 +4642,65 @@
         <v>53</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E21" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="F21" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>200</v>
-      </c>
       <c r="I21" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L21" s="29"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="8"/>
       <c r="B22" s="24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E22" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>204</v>
-      </c>
       <c r="I22" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" s="29"/>
     </row>
@@ -4679,996 +4708,1002 @@
       <c r="A23" s="8"/>
       <c r="B23" s="25"/>
       <c r="C23" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>207</v>
-      </c>
       <c r="I23" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K24" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L24" s="29"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E25" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" s="22" t="s">
         <v>213</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>212</v>
       </c>
       <c r="I25" s="22"/>
       <c r="J25" s="22"/>
       <c r="K25" s="27"/>
       <c r="L25" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G26" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>217</v>
-      </c>
       <c r="H26" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L27" s="29"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D28" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>227</v>
-      </c>
       <c r="H28" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K28" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L28" s="29"/>
       <c r="O28" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D29" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>231</v>
-      </c>
       <c r="H29" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L29" s="29"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D30" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>235</v>
-      </c>
       <c r="H30" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K30" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L30" s="29"/>
+      <c r="N30" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E31" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>239</v>
-      </c>
       <c r="H31" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L31" s="29"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="8"/>
       <c r="B33" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K33" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="8"/>
       <c r="B34" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K34" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L34" s="29"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="8"/>
       <c r="B35" s="20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K35" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>251</v>
+        <v>253</v>
+      </c>
+      <c r="M35" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8"/>
       <c r="B36" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="C36" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>250</v>
-      </c>
       <c r="G36" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K36" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L36" s="29"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="8"/>
       <c r="B37" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K37" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L37" s="29"/>
-      <c r="N37" t="s">
-        <v>260</v>
+      <c r="N37" s="45" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="8"/>
       <c r="B38" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C38" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="D38" s="22" t="s">
-        <v>258</v>
-      </c>
       <c r="E38" s="22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K38" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L38" s="29"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="8"/>
       <c r="B39" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K39" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L39" s="29"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="8"/>
       <c r="B40" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K40" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L40" s="29" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8"/>
       <c r="B41" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K41" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L41" s="29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="8"/>
       <c r="B42" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K42" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L42" s="29"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="8"/>
       <c r="B43" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K43" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L43" s="29"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="8"/>
       <c r="B44" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K44" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L44" s="29"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="8"/>
       <c r="B45" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K45" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L45" s="29"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="8"/>
       <c r="B46" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K46" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L46" s="29"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="8"/>
       <c r="B47" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K47" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L47" s="29"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="8"/>
       <c r="B48" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K48" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L48" s="29"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="8"/>
       <c r="B49" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K49" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L49" s="29"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="8"/>
       <c r="B50" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K50" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L50" s="29"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="8"/>
       <c r="B51" s="20" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K51" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L51" s="29"/>
     </row>
@@ -5678,31 +5713,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K52" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L52" s="29"/>
     </row>
@@ -5712,446 +5747,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J53" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K53" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L53" s="29"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="8"/>
       <c r="B54" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K54" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L54" s="29"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="8"/>
       <c r="B55" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K55" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L55" s="29"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="8"/>
       <c r="B56" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K56" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L56" s="29"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="8"/>
       <c r="B57" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K57" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L57" s="29"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="8"/>
       <c r="B58" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="H58" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="I58" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="D58" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>290</v>
-      </c>
       <c r="J58" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K58" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L58" s="29"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="8"/>
       <c r="B59" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J59" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K59" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L59" s="29"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="8"/>
       <c r="B60" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K60" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L60" s="29"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="8"/>
       <c r="B61" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K61" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L61" s="29"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="8"/>
       <c r="B62" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K62" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L62" s="29"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="8"/>
       <c r="B63" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J63" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K63" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L63" s="29"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="8"/>
       <c r="B64" s="20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J64" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K64" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L64" s="29"/>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:15">
       <c r="A65" s="8"/>
       <c r="B65" s="20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K65" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L65" s="29"/>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:15">
       <c r="A66" s="8"/>
       <c r="B66" s="24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -6163,9 +6198,11 @@
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:15">
       <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
+      <c r="B67" s="8" t="s">
+        <v>307</v>
+      </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -6175,10 +6212,15 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="O67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
+      <c r="B68" s="8" t="s">
+        <v>308</v>
+      </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -6188,8 +6230,11 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="O68" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -6202,7 +6247,7 @@
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:15">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -6215,7 +6260,7 @@
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:15">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -6228,7 +6273,7 @@
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:15">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -6241,7 +6286,7 @@
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:15">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -6254,7 +6299,7 @@
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:15">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -6267,7 +6312,7 @@
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:15">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -6280,7 +6325,7 @@
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:15">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -6293,7 +6338,7 @@
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:15">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -6306,7 +6351,7 @@
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:15">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -6319,7 +6364,7 @@
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:15">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -6332,7 +6377,7 @@
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:15">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -6375,13 +6420,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -6390,12 +6435,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C2" t="s">
         <v>69</v>
@@ -6406,12 +6451,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
@@ -6422,12 +6467,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
@@ -6441,15 +6486,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
@@ -6460,12 +6505,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -6478,7 +6523,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
@@ -6491,7 +6536,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
@@ -6504,7 +6549,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -6517,7 +6562,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -6529,7 +6574,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C11" t="s">
         <v>72</v>
@@ -7038,13 +7083,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -7053,13 +7098,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -7068,13 +7113,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -7083,13 +7128,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -7098,13 +7143,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -7113,13 +7158,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -7128,13 +7173,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -7143,25 +7188,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -7176,7 +7221,7 @@
         <v>69</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -7191,43 +7236,43 @@
         <v>72</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -7239,10 +7284,10 @@
         <v>69</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -7253,10 +7298,10 @@
         <v>72</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -7267,10 +7312,10 @@
         <v>69</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -7281,10 +7326,10 @@
         <v>72</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -7295,10 +7340,10 @@
         <v>69</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7309,10 +7354,10 @@
         <v>72</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7323,10 +7368,10 @@
         <v>69</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7337,10 +7382,10 @@
         <v>72</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7351,10 +7396,10 @@
         <v>69</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -7365,10 +7410,10 @@
         <v>72</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -7379,10 +7424,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7393,10 +7438,10 @@
         <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7407,10 +7452,10 @@
         <v>69</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7421,10 +7466,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -7435,10 +7480,10 @@
         <v>69</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -7449,10 +7494,10 @@
         <v>72</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -7463,10 +7508,10 @@
         <v>69</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -7477,10 +7522,10 @@
         <v>72</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -7491,10 +7536,10 @@
         <v>69</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -7505,10 +7550,10 @@
         <v>72</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -7522,7 +7567,7 @@
         <v>85</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -7536,758 +7581,758 @@
         <v>85</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C80" t="s">
         <v>72</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C81" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C82" t="s">
         <v>69</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C83" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C84" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C85" t="s">
         <v>69</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C86" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C87" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C88" t="s">
         <v>69</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C89" t="s">
         <v>72</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C90" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C91" t="s">
         <v>69</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C92" t="s">
         <v>72</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C93" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C94" t="s">
         <v>69</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C95" t="s">
         <v>72</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C97" t="s">
         <v>69</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C98" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C99" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C101" t="s">
         <v>72</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C102" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C103" t="s">
         <v>69</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E103" s="32"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C104" t="s">
         <v>72</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C105" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C106" t="s">
         <v>69</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E106" s="32"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C107" t="s">
         <v>72</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C108" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E108" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C109" t="s">
         <v>69</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E109" s="32"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C110" t="s">
         <v>72</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s">
         <v>69</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C113" t="s">
         <v>72</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C114" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E114" s="32" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C115" t="s">
         <v>69</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C116" t="s">
         <v>72</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C117" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C120" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C122" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C123" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D123" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D125" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C126" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D126" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C127" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D127" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C128" t="s">
+        <v>370</v>
+      </c>
+      <c r="D128" t="s">
         <v>365</v>
-      </c>
-      <c r="D128" t="s">
-        <v>360</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D129" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C130" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D130" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C131" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D131" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C132" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D132" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C134" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D134" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C135" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D135" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D136" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C137" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D137" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C139" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D139" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -8815,7 +8860,7 @@
         <v>85</v>
       </c>
       <c r="B186" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
         <v>69</v>
@@ -8832,7 +8877,7 @@
         <v>85</v>
       </c>
       <c r="B187" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C187" t="s">
         <v>72</v>
@@ -8886,7 +8931,7 @@
         <v>94</v>
       </c>
       <c r="C190" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>92</v>
@@ -9342,71 +9387,71 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="12" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -9414,13 +9459,13 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -9428,7 +9473,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H5" s="8"/>
     </row>
@@ -9437,16 +9482,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" s="8"/>
     </row>
@@ -9455,16 +9500,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -9473,16 +9518,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H8" s="8"/>
     </row>
@@ -9491,16 +9536,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -9509,16 +9554,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="13" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H10" s="8"/>
     </row>
@@ -9527,16 +9572,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="13" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -9545,16 +9590,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H12" s="8"/>
     </row>
@@ -9563,16 +9608,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H13" s="8"/>
     </row>
@@ -9581,16 +9626,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -9599,22 +9644,22 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9622,23 +9667,23 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H17" s="8"/>
     </row>
@@ -9647,18 +9692,18 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H18" s="8"/>
     </row>
@@ -9667,18 +9712,18 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H19" s="8"/>
     </row>
@@ -9687,20 +9732,20 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H20" s="8"/>
     </row>
@@ -9709,20 +9754,20 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H21" s="8"/>
     </row>
@@ -9731,20 +9776,20 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H22" s="8"/>
     </row>
@@ -9753,44 +9798,44 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H24" s="8"/>
     </row>
